--- a/research/brics_universities/output/BRICS_universities_india.xlsx
+++ b/research/brics_universities/output/BRICS_universities_india.xlsx
@@ -558,10 +558,10 @@
         <v>154</v>
       </c>
       <c r="G5" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H5" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="AD47" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="AE47" s="4" t="inlineStr">
@@ -16795,20 +16795,20 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>adidir@nitt.edu</t>
+          <t>deanid@nitt.edu</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
-Заместитель декана по международным связям (Associate Dean, International Relations)
-Офис международных связей (Office of International Relations), зам. декана по международным связям
-Обращение: Dear Associate Dean of International Relations,</t>
+          <t>Dr. G. Uma
+Декан по институциональному развитию и связям с выпускниками (Dean, Institutional Development &amp; Alumni Relations)
+Декан по институциональному развитию и связям с выпускниками (Dean ID&amp;AR), курирует Office of International Relations
+Обращение: Dear Dr. Uma,</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>adidir@nitt.edu</t>
+          <t>deanid@nitt.edu</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>Prof. G. Aghila</t>
+          <t>Dr. G. Aghila</t>
         </is>
       </c>
       <c r="Q66" s="4" t="inlineStr">
@@ -16871,15 +16871,17 @@
       </c>
       <c r="AE66" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF66" s="4" t="inlineStr">
         <is>
-          <t>• Сайт nitt.edu недоступен (503) при проверке; директор, e-mail и телефоны взяты из поисковых сниппетов страниц nitt.edu — перепроверить
-• Директор Prof. G. Aghila вступила в должность 03.02.2022 (срок 5 лет — до ~02.2027)
-• Офис международных связей (OIR) подчинён декану по институциональному развитию и связям с выпускниками (Dean ID&amp;AR, Dr. G. Uma, deanid@nitt.edu); на старой странице OIR зам. декана — Dr. Ezhilarasi, в сниппете поиска — Dr. S. Nivethitha (adidir@nitt.edu); имя не подтверждено
-• Спутников не найдено</t>
+          <t>• Директор Prof. G. Aghila вступила в должность 03.02.2022 (срок 5 лет — до ~02.2027)
+• Спутников не найдено
+• Сайт доступен по http://www.nitt.edu (https — нет). 04.10.2026 подтверждены: директор Dr. G. Aghila и director@nitt.edu (страница Director), адрес Tiruchirappalli 620015 (Contact Us), декан ID&amp;AR Dr. G. Uma — deanid@nitt.edu / guma@nitt.edu, тел. +91-431-2503033 (страница Deans); телефоны по схеме +91-431-250xxxx (справочник 03.2026)
+• На главной странице объявлен конкурс на должность директора NIT Trichy (октябрь 2026) — срок Dr. Aghila истекает, перед рассылкой проверить смену руководителя
+• Ящик зам. декана по международным связям adidir@nitt.edu (по старому сниппету, Dr. S. Nivethitha / Dr. Ezhilarasi) не подтверждён — можно поставить в копию
+• Перепроверка: Директор, e-mail директора, адрес и декан ID&amp;AR (deanid@nitt.edu) подтверждены на сайте nitt.edu 04.10.2026; адресат изменён на Dr. G. Uma</t>
         </is>
       </c>
       <c r="AG66" s="4" t="inlineStr">
@@ -18411,11 +18413,12 @@
       </c>
       <c r="AF76" s="4" t="inlineStr">
         <is>
-          <t>• Сайт manit.ac.in недоступен (503 / сброс соединения) — контакты взяты из поискового индекса страницы manit.ac.in/deans, требуют перепроверки
-• Директор подтверждён только сторонней страницей конференции ICAMMT-2026
+          <t>• Сайт manit.ac.in и conf.manit.ac.in по-прежнему недоступны (таймаут/503, в т.ч. через WebFetch, 04.10.2026) — контакты взяты из поискового индекса страницы manit.ac.in/deans, требуют перепроверки
+• Директор Dr. Karunesh Kumar Shukla — по сторонней странице ICAMMT-2026 и по поисковому индексу официальной брошюры MANIT (ASDG 2026, май 2026: «Patron Dr. Karunesh Kumar Shukla») — сам документ открыть не удалось
 • Телефон +91 755 405 1021 — это телефон Dean ID&amp;IR, а не общий
 • Международные связи ведёт Dean (Institutional Development &amp; International Relations) Dr. Anupama Sharma; associate dean Dr. Jaytrilok Choudhary (jaytrilok@manit.ac.in)
-• Спутник AZAD-1 отменён (nanosats.eu)</t>
+• Спутник AZAD-1 отменён (nanosats.eu)
+• Перепроверка: Сайт недоступен; директор дополнительно подтверждён по индексу официальной брошюры 05.2026, контакты не изменены</t>
         </is>
       </c>
       <c r="AG76" s="4" t="inlineStr">
@@ -18858,10 +18861,12 @@
       </c>
       <c r="AF79" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт andhrauniversity.edu.in блокирует автоматический доступ (сброс соединения / HTTP 503); ФИО ректора, e-mail и телефон взяты из поисковой выдачи по официальным страницам VC Desk и International Affairs — перед отправкой проверить вручную
+          <t>• Официальный сайт andhrauniversity.edu.in по-прежнему недоступен (таймаут / HTTP 503, в т.ч. через WebFetch, 04.10.2026); ФИО ректора, e-mail и телефон взяты из поисковой выдачи по официальным страницам VC Desk и International Affairs — перед отправкой проверить вручную
+• Проф. G. P. Raja Sekhar (IIT Kharagpur) назначен ВК на трёхлетний срок (по СМИ ap7am.com, 2025) — на 2026 г. полномочия, вероятно, действуют
 • Декан по международным делам не подтверждён: в источниках встречаются Prof. S. Paul Douglas (Dean, International Affairs) и Prof. E. N. Dhananjay Rao (Dean, International Affairs and Public Relations) — имя адресата оставлено пустым
 • Почтовый адрес не проверен (ожидаемо: Andhra University, Visakhapatnam, Andhra Pradesh 530003) — заполнить после ручной проверки
-• Быстрая проверка спутников результата не дала; в nanosats.eu вуз не значится</t>
+• Быстрая проверка спутников результата не дала; в nanosats.eu вуз не значится
+• Перепроверка: Сайт недоступен; данные не изменены (ВК подтверждён только СМИ о назначении на 3-летний срок)</t>
         </is>
       </c>
       <c r="AG79" s="4" t="inlineStr">
@@ -19005,7 +19010,8 @@
           <t>• Сайт bdu.ac.in недоступен для автоматического доступа (сброс соединения / HTTP 503); e-mail vc@bdu.ac.in, irc@bdu.ac.in и телефон секретариата ректора взяты из поисковой выдачи по официальным страницам — проверить вручную
 • Должность ректора вакантна (Wikipedia: Vacant); вузом руководит Vice-Chancellor Committee, по данным поиска конвинер — E. Sundaravalli, I.A.S. (не подтверждено на открытой странице). Письмо адресовать на должность
 • Почтовый адрес не проверен (ожидаемо: Palkalaiperur, Tiruchirappalli 620 024, Tamil Nadu)
-• Быстрая проверка спутников (nanosats.eu, India) результата не дала</t>
+• Быстрая проверка спутников (nanosats.eu, India) результата не дала
+• Перепроверка: Сайт bdu.ac.in недоступен (curl — нет соединения, WebFetch 503) 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG80" s="4" t="inlineStr">
@@ -19128,7 +19134,9 @@
 • Имя ректора (VC) Dr. Vivek Saoji — по Википедии; по сайту не подтверждено
 • По поисковой выдаче (не проверено на открытой странице): Office of International Affairs возглавляет Prof. Dr. Kirti Mahajan; адрес офиса — Bharati Vidyapeeth Bhavan, Lal Bahadur Shastri Marg, Pune 411030
 • Частный многопрофильный deemed-университет с кампусами в Пуне, Нью-Дели, Нави-Мумбаи, Сангли, Колхапуре и др
-• Запущенных спутников не найдено (проверка по nanosats.eu и списку ISRO Student Satellites)</t>
+• Запущенных спутников не найдено (проверка по nanosats.eu и списку ISRO Student Satellites)
+• Повторная проверка 04.10.2026: по поисковой выдаче Prof. Dr. Vivek A. Saoji — VC с 01.10.2022, директор Office of International Affairs (bvuniversity.edu.in/isc/) — Prof. Dr. Kirti Mahajan; страницы открыть не удалось
+• Перепроверка: Сайты bvuniversity.edu.in (Cloudflare 403) и *.bharatividyapeeth.edu (сброс соединения) недоступны 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG81" s="4" t="inlineStr">
@@ -20732,7 +20740,8 @@
         <is>
           <t>• САЙТ ЗАБЛОКИРОВАН: у mmmut.ac.in истёк SSL-сертификат, WebFetch — 503; контакты не проверены, адрес/e-mail оставлены пустыми
 • Ректор указан только по Википедии (без учёного звания) — требуется проверка перед рассылкой
-• Спутниковых проектов в nanosats.eu нет</t>
+• Спутниковых проектов в nanosats.eu нет
+• Перепроверка: 04.10.2026: mmmut.ac.in по-прежнему недоступен (ошибка сертификата; WebFetch — 503); данные не изменены</t>
         </is>
       </c>
       <c r="AG92" s="4" t="inlineStr">
@@ -22379,7 +22388,8 @@
           <t>• Официальный сайт mzu.edu.in недоступен (ошибка SSL-сертификата / HTTP 503) — данные ISCC взяты из поискового индекса страницы ISCC, не открыты напрямую
 • Ректор Prof. Dibakar Chandra Deka вступил в должность 1 мая 2023 г. (пресс-релиз DIPR Mizoram); подтверждения на 2025–2026 с официального сайта получить не удалось
 • Международные связи: International Students Centre and Collaborations (ISCC); имя директора не установлено; зам. директора — Dr. Laltanpuii Ralte (tanpuii@mzu.edu.in) — по данным поискового индекса
-• LIGHT-проверка: спутниковых проектов не найдено</t>
+• LIGHT-проверка: спутниковых проектов не найдено
+• Перепроверка: Сайт mzu.edu.in по-прежнему недоступен (ошибка TLS-сертификата), DIPR Mizoram — 403; данные не изменены</t>
         </is>
       </c>
       <c r="AG103" s="4" t="inlineStr">
@@ -23985,11 +23995,12 @@
       </c>
       <c r="AF114" s="4" t="inlineStr">
         <is>
-          <t>• Сайт iitj.ac.in недоступен (503) при проверке; контакты офиса международных связей взяты из поискового сниппета — перепроверить
+          <t>• Сайт iitj.ac.in недоступен (503, затем блокировка WAF при повторной проверке 04.10.2026); контакты офиса международных связей взяты из поискового сниппета — перепроверить
 • Декан по международным связям по сниппету — Dr. Ankur Gupta (doir@iitj.ac.in); общий ящик office_ir@iitj.ac.in; не подтверждено открытой страницей
 • Директор Prof. Avinash Kumar Agarwal — с 01.05.2024 на 5 лет (подтверждено постом IIT Jodhpur в X, сентябрь 2025)
 • Телефон указан офиса международных связей
-• Упоминается прототип CubeSat SABHASAT (гамма-всплески) с участием IIT Jodhpur — не подтверждено; спутников на орбите нет</t>
+• Упоминается прототип CubeSat SABHASAT (гамма-всплески) с участием IIT Jodhpur — не подтверждено; спутников на орбите нет
+• Перепроверка: Сайт iitj.ac.in (после исправления цепочки сертификата) отдаёт страницу блокировки WAF («This page can't be displayed») — контакты не подтверждены, данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG114" s="4" t="inlineStr">
@@ -25393,7 +25404,8 @@
 • По Википедии: частный автономный колледж (основатель — Shiv Nadar); с 2026–27 уч. г. переходит в состав Shiv Nadar University, Chennai как SSN School of Engineering — письмо, возможно, лучше адресовать Shiv Nadar University Chennai
 • Имя директора (Dr. S. Radha) — по Википедии, не подтверждено на официальном сайте
 • По поисковой выдаче (не проверено): principal@ssn.edu.in, info@ssn.edu.in, +91-44-27469700
-• Запущенных спутников не найдено (проверка по nanosats.eu и списку ISRO Student Satellites)</t>
+• Запущенных спутников не найдено (проверка по nanosats.eu и списку ISRO Student Satellites)
+• Перепроверка: Сайт ssn.edu.in (включая /contact-us/) и сайты Shiv Nadar University по-прежнему недоступны (Cloudflare 403/502); данные не изменены</t>
         </is>
       </c>
       <c r="AG124" s="4" t="inlineStr">
@@ -25786,7 +25798,9 @@
         <is>
           <t>• Сайт kashmiruniversity.net заблокирован/недоступен (сброс соединения) – контакты не проверены
 • По поисковой выдаче: registrar@kashmiruniversity.ac.in, info@kashmiruniversity.net – не подтверждены, перед отправкой проверить
-• Срок полномочий VC Prof. Nilofer Khan продлён на 2 года с 19.05.2025 (до мая 2027)</t>
+• Срок полномочий VC Prof. Nilofer Khan продлён на 2 года с 19.05.2025 (до мая 2027)
+• Повторная проверка 10.2026: сайт по-прежнему недоступен (сброс соединения / 403); по поиску VC Prof. Nilofer Khan продолжала работу в октябре 2026 г., срок — до 05.2027
+• Перепроверка: 04.10.2026: kashmiruniversity.net недоступен; ректор подтверждается только СМИ/поиском — данные не изменены</t>
         </is>
       </c>
       <c r="AG127" s="4" t="inlineStr">
@@ -25850,10 +25864,25 @@
           <t>University of Madras, Chepauk, Chennai 600 005, Tamil Nadu, India</t>
         </is>
       </c>
-      <c r="J128" s="4" t="inlineStr"/>
-      <c r="K128" s="4" t="inlineStr"/>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>registrar@unom.ac.in</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Rita John
+Registrar
+Регистратор (Registrar)
+Обращение: Dear Professor John,</t>
+        </is>
+      </c>
       <c r="L128" s="4" t="inlineStr"/>
-      <c r="M128" s="4" t="inlineStr"/>
+      <c r="M128" s="4" t="inlineStr">
+        <is>
+          <t>registrar@unom.ac.in</t>
+        </is>
+      </c>
       <c r="N128" s="4" t="inlineStr">
         <is>
           <t>+91 44 2539 9422</t>
@@ -25864,7 +25893,11 @@
           <t>https://www.unom.ac.in</t>
         </is>
       </c>
-      <c r="P128" s="4" t="inlineStr"/>
+      <c r="P128" s="4" t="inlineStr">
+        <is>
+          <t>Thiru V. Arun Roy, I.A.S. (Convener, VC Convener Committee)</t>
+        </is>
+      </c>
       <c r="Q128" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor (вакантно; управляет VC Convener Committee)</t>
@@ -25894,17 +25927,22 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD128" s="4" t="inlineStr"/>
+      <c r="AD128" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE128" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF128" s="4" t="inlineStr">
         <is>
-          <t>• Должность ректора вакантна: после окончания срока Prof. S. Gowri университетом управляет комитет; конвинер — Thiru V. Arun Roy, I.A.S. (секретарь Департамента высшего образования Тамилнада)
-• Регистратор: Prof. Dr. Rita John
-• На сайте нет e-mail руководства и международного офиса (только webteam@unom.ac.in) — нужен альтернативный канал</t>
+          <t>• Должность вице-канцлера вакантна: после окончания срока Prof. S. Gowri университетом управляет VC Convener Committee; конвинер — Thiru V. Arun Roy, I.A.S. (секретарь Департамента высшего образования Тамилнада) — по официальной странице (без даты)
+• Регистратор: Prof. Dr. Rita John, registrar@unom.ac.in (альт. registrar.unom@gmail.com) — официальная страница Registrar
+• Ящик vcunom@unom.ac.in принадлежит офису вице-канцлера (при вакансии адресата нет); отдельного e-mail международного офиса на сайте не найдено
+• Перепроверка: На официальном сайте unom.ac.in (открыт 04.10.2026) подтверждены: управление VC Convener Committee (конвинер V. Arun Roy, I.A.S.), регистратор Prof. Rita John и её e-mail registrar@unom.ac.in; страницы без даты</t>
         </is>
       </c>
       <c r="AG128" s="4" t="inlineStr">
@@ -26207,7 +26245,8 @@
 • Это составной колледж Andhra University; ректор университета — Prof. G. P. Raja Sekhar (vicechancellor@andhrauniversity.edu.in, +91 891 2844222 — по поисковому индексу); принципал Prof. M. Shashi подтверждён новостью Yo! Vizag (август 2026)
 • Офис международных связей колледжа/университета не установлен
 • LIGHT-проверка: спутниковых проектов не найдено
-• Почтовый индекс не проверен</t>
+• Почтовый индекс не проверен
+• Перепроверка: Сайт andhrauniversity.edu.in недоступен (сброс/503, 04.10.2026, curl и WebFetch); данные не изменены</t>
         </is>
       </c>
       <c r="AG130" s="4" t="inlineStr">
@@ -26627,7 +26666,8 @@
         <is>
           <t>• Сайт gitam.edu блокирует автоматический доступ (HTTP 403) — контакты не проверены; лимит веб-поиска сессии исчерпан. Ректор указан по Wikipedia — проверить вручную
 • Кампусы: Висакхапатнам (Rushikonda, основной), Хайдарабад, Бенгалуру; по Wikipedia адрес основного кампуса — Gandhi Nagar, Rushikonda, Visakhapatnam 530045 (не проверен на официальном сайте)
-• Быстрая проверка спутников (nanosats.eu, India) результата не дала</t>
+• Быстрая проверка спутников (nanosats.eu, India) результата не дала
+• Перепроверка: gitam.edu по-прежнему отдаёт анти-бот-защиту HTTP 403 (04.10.2026); обход не выполнялся, данные не изменены</t>
         </is>
       </c>
       <c r="AG133" s="4" t="inlineStr">
@@ -28059,7 +28099,7 @@
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
-          <t>+91-11-25099017</t>
+          <t>+91 11 2509 9017 (reception helpline)</t>
         </is>
       </c>
       <c r="O143" s="4" t="inlineStr">
@@ -28112,21 +28152,24 @@
       </c>
       <c r="AE143" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF143" s="4" t="inlineStr">
         <is>
-          <t>• Сайт nsut.ac.in недоступен (503/таймаут) при проверке; контакты и имя VC взяты из поисковых сниппетов — перепроверить
+          <t>• E-mail vc@nsut.ac.in взят из поисковых сниппетов — на открытых страницах сайта (VC, Contact Us) не найден; на странице контактов только адреса отделов (ar.acad@nsut.ac.in — академический отдел)
 • Офис международных связей/декан по международным делам не найден
-• Спутников не найдено</t>
+• Спутников не найдено
+• Перепроверка: Проректор (VC) проф. Ананд Шривастава (с 29.11.2023), адрес и телефон подтверждены на nsut.ac.in 04.10.2026; vc@nsut.ac.in на открытых страницах не найден</t>
         </is>
       </c>
       <c r="AG143" s="4" t="inlineStr">
         <is>
           <t>• Https://nsut.ac.in/en/contact-us
 • Https://en.wikipedia.org/wiki/Netaji_Subhas_University_of_Technology
-• Nanosats.eu</t>
+• Nanosats.eu
+• Https://www.nsut.ac.in/en/vice-chancellor
+• Https://www.nsut.ac.in/en/contact-us</t>
         </is>
       </c>
       <c r="AH143" s="4" t="inlineStr">
@@ -29060,15 +29103,42 @@
 • Technology</t>
         </is>
       </c>
-      <c r="I150" s="4" t="inlineStr"/>
-      <c r="J150" s="4" t="inlineStr"/>
-      <c r="K150" s="4" t="inlineStr"/>
-      <c r="L150" s="4" t="inlineStr"/>
-      <c r="M150" s="4" t="inlineStr"/>
-      <c r="N150" s="4" t="inlineStr"/>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>Assam University, Silchar - 788011, Assam, India</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>barunjyotichoudhury@gmail.com</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Barunjyoti Choudhury
+Director, Directorate for Internationalization of Higher Education
+Директорат интернационализации высшего образования (Directorate for Internationalization of Higher Education) — директор
+Обращение: Dear Dr. Choudhury,</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>barunjyotichoudhury@gmail.com</t>
+        </is>
+      </c>
+      <c r="M150" s="4" t="inlineStr">
+        <is>
+          <t>registrar@aus.ac.in</t>
+        </is>
+      </c>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>+91 3842 270806</t>
+        </is>
+      </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>http://www.aus.ac.in</t>
+          <t>https://www.aus.ac.in</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
@@ -29105,23 +29175,33 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD150" s="4" t="inlineStr"/>
+      <c r="AD150" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE150" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF150" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт aus.ac.in на момент проверки (02.10.2026) неработоспособен — перенаправляет на страницу установки WordPress (wp-admin/setup-config.php); контакты не удалось проверить, лимит веб-поиска исчерпан
-• Ректор указан по Wikipedia (Prof. Rajive Mohan Pant) — требуется ручная проверка
-• Быстрая проверка спутников (nanosats.eu, India) результата не дала</t>
+          <t>• Ректор указан по Wikipedia (Prof. Rajive Mohan Pant) — требуется ручная проверка
+• Быстрая проверка спутников (nanosats.eu, India) результата не дала
+• Сайт aus.ac.in снова доступен (04.10.2026, частично с ошибкой WordPress): страница контактов — адрес, тел. 03842-270806, факс 03842-270802, vc@aus.ac.in, registrar@aus.ac.in
+• Директорат интернационализации: Working Chairman Prof. Dipendu Das (dipendudas2011@gmail.com, +91-9435172416), Director Dr. Barunjyoti Choudhury (barunjyotichoudhury@gmail.com, +91-7002415050), Deputy Director Dr. Biswa Ranjan Roy (brroy88@gmail.com) — на официальной странице указаны личные gmail-адреса; для копии можно использовать vc@aus.ac.in
+• Имя ректора на открытых страницах сайта (Who's Who без раздела руководства) не найдено
+• Перепроверка: Сайт открылся 04.10.2026: подтверждены адрес, телефон, vc@/registrar@aus.ac.in и контакты Директората интернационализации; ректор по-прежнему не подтверждён</t>
         </is>
       </c>
       <c r="AG150" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Assam_University
-• Http://www.aus.ac.in</t>
+• Http://www.aus.ac.in
+• Https://www.aus.ac.in/contactus/
+• Https://www.aus.ac.in/internationalization-of-higher-education/
+• Https://www.aus.ac.in/whos-who/</t>
         </is>
       </c>
       <c r="AH150" s="4" t="inlineStr">
@@ -29660,7 +29740,8 @@
           <t>• Официальные сайты (bangaloreuniversity.karnataka.gov.in, bangaloreuniversity.ac.in) недоступны (503 / таймаут) — контакты не подтверждены
 • Ректор (VC) C. Shivaraju назначен 12.07.2026 (по Википедии); учёное звание на официальном сайте не проверено
 • По поисковой выдаче (не проверено): адрес — Jnanabharathi Campus, Bengaluru 560056
-• Запущенных спутников не найдено (проверка по nanosats.eu и списку ISRO Student Satellites)</t>
+• Запущенных спутников не найдено (проверка по nanosats.eu и списку ISRO Student Satellites)
+• Перепроверка: Сайт bangaloreuniversity.karnataka.gov.in и портал karnataka.gov.in недоступны (503 / сброс соединения), домен bangaloreuniversity.ac.in не разрешается — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG154" s="4" t="inlineStr">
@@ -30188,7 +30269,7 @@
       </c>
       <c r="N158" s="4" t="inlineStr">
         <is>
-          <t>+91-95922-14444</t>
+          <t>+91-95922-14444; 1800-2003575 (toll-free); Dean International Affairs: +91 97819 25259</t>
         </is>
       </c>
       <c r="O158" s="4" t="inlineStr">
@@ -30237,14 +30318,15 @@
       </c>
       <c r="AE158" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF158" s="4" t="inlineStr">
         <is>
-          <t>• Противоречие на сайте: страница «Important Contacts» называет Director-Principal Dr. Sukhpreet Kaur, а страница послания – Dr. Rajdeep Singh; уточнить
+          <t>• Страница «Important Contacts» называет Director-Principal Dr. Sukhpreet Kaur; Dr. Rajdeep Singh — Campus Director CGC Landran (страница campus-director-message), но его имя также осталось на странице director-principal-message (вероятно, устаревшей) — перед рассылкой уточнить. Даты на страницах не указаны
 • Опубликован только admissions@cgc.edu.in; сайт cgc.edu.in закрыт JS-защитой от ботов
-• Декан по международным делам – Dr. Ramandeep Saini (тел. 9781925259, email не опубликован)</t>
+• Декан по международным делам – Dr. Ramandeep Saini (тел. 9781925259, email не опубликован)
+• Перепроверка: Сайт cecmohali.org повторно открыт 04.10.2026: Director-Principal Dr. Sukhpreet Kaur, декан по междунар. делам Dr. Ramandeep Saini, адрес и admissions@cgc.edu.in подтверждены; противоречие с Dr. Rajdeep Singh объяснено частично (он — Campus Director CGC Landran)</t>
         </is>
       </c>
       <c r="AG158" s="4" t="inlineStr">
@@ -31210,16 +31292,18 @@
       </c>
       <c r="AF165" s="4" t="inlineStr">
         <is>
-          <t>• Сайт iitbhilai.ac.in при проверке недоступен (503 / таймаут) — контакты не подтверждены
-• Директор проф. Rajiv Prakash назначен в сентябре 2022 г. (новость Central Chronicle); актуальность на 2025–2026 по официальному сайту не подтверждена
+          <t>• Сайт iitbhilai.ac.in при проверке недоступен (503 / ошибка TLS, повторно 04.10.2026) — контакты не подтверждены
+• Директор проф. Rajiv Prakash (в должности с 26.09.2022) — действующий по публикации официального аккаунта IIT Bhilai в X от 08.06.2026
 • По поисковой выдаче (не проверено на открытой странице): director@iitbhilai.ac.in, administration@iitbhilai.ac.in
-• Запущенных спутников не найдено (проверка по nanosats.eu и списку ISRO Student Satellites)</t>
+• Запущенных спутников не найдено (проверка по nanosats.eu и списку ISRO Student Satellites)
+• Перепроверка: Директор проф. Rajiv Prakash подтверждён официальным аккаунтом IIT Bhilai в X (08.06.2026); сайт по-прежнему недоступен (503) — контакты не подтверждены</t>
         </is>
       </c>
       <c r="AG165" s="4" t="inlineStr">
         <is>
           <t>• Https://centralchronicle.in/prof-rajiv-prakash-appointed-as-director-of-iit-bhilai/
-• Https://www.isro.gov.in/StudentSatellite.html</t>
+• Https://www.isro.gov.in/StudentSatellite.html
+• Https://x.com/IIT_Bhilai/status/2063967770812047649</t>
         </is>
       </c>
       <c r="AH165" s="4" t="inlineStr">
@@ -31637,7 +31721,8 @@
         <is>
           <t>• Сайт imu.edu.in недоступен из нашей сети (ошибка TLS-сертификата / 503) – данные взяты из поисковой выдачи официальной страницы VC, требуют перепроверки
 • Dr. Malini V. Shankar (IAS в отставке) – срок её полномочий может истекать в 2026 г.; уточнить перед отправкой
-• Профиль морской; космической активности не найдено</t>
+• Профиль морской; космической активности не найдено
+• Перепроверка: Сайт imu.edu.in недоступен (curl — нет соединения, WebFetch 503) 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG168" s="4" t="inlineStr">
@@ -31777,7 +31862,8 @@
           <t>• Сайт iiitd.ac.in недоступен (ошибка цепочки TLS-сертификата / HTTP 503); директор подтверждён новостью BW Education от 01.08.2026; e-mail директора и международного офиса — из поисковой выдачи по официальным страницам, проверить вручную
 • Международные дела: Faculty In-Charge — Dr. Anuj Grover (личный e-mail); общий ящик международного отдела по приёму — int-admissions@iiitd.ac.in
 • Почтовый адрес не проверен (ожидаемо: Okhla Industrial Estate, Phase III, New Delhi 110020)
-• Быстрая проверка спутников (nanosats.eu, India) результата не дала</t>
+• Быстрая проверка спутников (nanosats.eu, India) результата не дала
+• Перепроверка: 04.10.2026: iiitd.ac.in и ia.iiitd.ac.in недоступны (ошибка TLS-цепочки); данные не изменены</t>
         </is>
       </c>
       <c r="AG169" s="4" t="inlineStr">
@@ -32447,10 +32533,11 @@
       </c>
       <c r="AF174" s="4" t="inlineStr">
         <is>
-          <t>• Сайт mkuniversity.ac.in недоступен (SSL-ошибка/503/отказ прокси); лимит веб-поиска исчерпан — контакты не проверены, поля оставлены пустыми
-• По Wikipedia должность ВК вакантна (вуз управляется комитетом/конвинером) — перед рассылкой установить текущего руководителя и почту
+          <t>• Сайт mkuniversity.ac.in (http/https, www, /new/) по-прежнему недоступен (SSL-ошибка / 503, 04.10.2026) — контакты не проверены, поля оставлены пустыми
+• По Wikipedia должность ВК вакантна (вуз управляется комитетом/конвинером); агрегатор timesofcollege указывает Prof. J. Kumar (ВК до 2024 г., вероятно устарело) — перед рассылкой установить текущего руководителя и почту
 • Почтовый адрес нужно дополнить (кампус Palkalai Nagar) после проверки на официальном сайте
-• Спутников в nanosats.csv нет</t>
+• Спутников в nanosats.csv нет
+• Перепроверка: Сайт недоступен; данные не изменены, текущий руководитель не установлен</t>
         </is>
       </c>
       <c r="AG174" s="4" t="inlineStr">
@@ -32594,7 +32681,8 @@
 • Офис международных связей и его e-mail не найдены; info@ — общий справочный ящик
 • Полный почтовый адрес не подтверждён
 • Частный университет штата Телангана (Mahindra Group, бывш. École Centrale School of Engineering)
-• Спутников не найдено</t>
+• Спутников не найдено
+• Перепроверка: Сайт mahindrauniversity.edu.in по-прежнему закрыт (403 Cloudflare, в т.ч. WebFetch и sitemap) на 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG175" s="4" t="inlineStr">
@@ -33023,7 +33111,9 @@
         <is>
           <t>• Сайт uni-mysore.ac.in заблокирован (ошибка SSL / 503) — имя и e-mail ректора взяты из списка Academic Council (июнь 2024) по данным поиска; требуется перепроверка актуальности на 2026
 • Международный офис не проверен
-• Космических проектов не найдено</t>
+• Космических проектов не найдено
+• Повторная проверка 10.2026: сайт недоступен (ошибка TLS-цепочки / 503); актуальность VC на 2026 г. по-прежнему не подтверждена
+• Перепроверка: 04.10.2026: uni-mysore.ac.in недоступен; новых официальных подтверждений не найдено — данные не изменены</t>
         </is>
       </c>
       <c r="AG178" s="4" t="inlineStr">
@@ -34512,7 +34602,7 @@
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
-          <t>director@nitpy.ac.in</t>
+          <t>thangavel.s@nitpy.ac.in</t>
         </is>
       </c>
       <c r="K189" s="4" t="inlineStr">
@@ -34523,13 +34613,21 @@
 Обращение: Dear Dr. Ghangrekar,</t>
         </is>
       </c>
-      <c r="L189" s="4" t="inlineStr"/>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>thangavel.s@nitpy.ac.in</t>
+        </is>
+      </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
           <t>director@nitpy.ac.in</t>
         </is>
       </c>
-      <c r="N189" s="4" t="inlineStr"/>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>+91 4368 265235 (доб. 101 — директор; доб. 334 — декан по международным связям); +91 4368 265230 (администрация)</t>
+        </is>
+      </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
           <t>https://nitpy.ac.in</t>
@@ -34537,7 +34635,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>Dr. Makarand Madhao Ghangrekar</t>
+          <t>Prof. Makarand Madhao Ghangrekar</t>
         </is>
       </c>
       <c r="Q189" s="4" t="inlineStr">
@@ -34576,13 +34674,16 @@
       </c>
       <c r="AE189" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF189" s="4" t="inlineStr">
         <is>
-          <t>• Сайт nitpy.ac.in заблокирован (ошибка SSL / 503) — данные о директоре и e-mail взяты из выдачи поиска по странице BoG, не открыты напрямую
-• Регистратор: Dr. S. Sundaravarathan, registrar@nitpy.ac.in</t>
+          <t>• Сайт nitpy.ac.in напрямую из нашей сети недоступен (ошибка SSL через прокси); страницы открыты через r.jina.ai 04.10.2026. E-mail на сайте записаны в виде name[at]nitpy[dot]ac[dot]in
+• Декан по международным связям, выпускникам и PR (Dean, International Relations, Alumni &amp; Publicity): Dr. Thangavel S (thangavel.s@nitpy.ac.in, доб. 334); заместители — Dr. Ansuman Mahapatra, Dr. Malaya Kumar Nath
+• Регистратор: Dr. S. Sundaravarathan, registrar@nitpy.ac.in (доб. 104)
+• Почтовый индекс на официальных страницах не указан (только «Karaikal, Puducherry»)
+• Перепроверка: Директор, e-mail директора и декан по международным связям подтверждены на nitpy.ac.in (Administration/Dean Directory, стр. от 01.10.2026) 04.10.2026 через reader-сервис; добавлены международный e-mail и телефоны</t>
         </is>
       </c>
       <c r="AG189" s="4" t="inlineStr">
@@ -34793,7 +34894,7 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>Pandit Deendayal Energy University, Gandhinagar, Gujarat, India</t>
+          <t>Pandit Deendayal Energy University, Knowledge Corridor, Raisan, Gandhinagar, Gujarat 382426, India</t>
         </is>
       </c>
       <c r="J191" s="4" t="inlineStr">
@@ -34803,10 +34904,10 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
-Декан по международным связям (Dean, International Relations)
+          <t>Prof. Ritu Sharma
+Head, Office of International Relations
 Офис международных связей (Office of International Relations), декан по международным связям
-Обращение: Dear Dean of International Relations,</t>
+Обращение: Dear Professor Sharma,</t>
         </is>
       </c>
       <c r="L191" s="4" t="inlineStr">
@@ -34817,12 +34918,12 @@
       <c r="M191" s="4" t="inlineStr"/>
       <c r="N191" s="4" t="inlineStr">
         <is>
-          <t>+91-79-23275223</t>
+          <t>+91 79 2327 5060 (general); +91 79 2327 5226 (Head, OIR)</t>
         </is>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>https://www.pdpu.ac.in</t>
+          <t>https://pdeu.ac.in</t>
         </is>
       </c>
       <c r="P191" s="4" t="inlineStr">
@@ -34866,23 +34967,25 @@
       </c>
       <c r="AE191" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF191" s="4" t="inlineStr">
         <is>
-          <t>• Сайт pdpu.ac.in недоступен (503) при проверке; все контакты из поискового сниппета страницы inter-contactus.html — перепроверить
+          <t>• Новый официальный домен — pdeu.ac.in (старый pdpu.ac.in недоступен, e-mail остаются в домене @pdpu.ac.in)
+• Контакты подтверждены на странице Contact Us: Head OIR — Prof. Ritu Sharma, Dean.IR@pdpu.ac.in, +91-79-23275226; ассистенты OIR — Rohit Mishra (rohit.mishra@pdpu.ac.in), Bhaunesh Shah (bhaunesh.shah@pdpu.ac.in)
+• Director General Prof. Sundar S. Manoharan — на главной странице официального сайта
+• Общий e-mail университета на странице контактов не опубликован (только телефон 079-23275060)
 • Ранее Pandit Deendayal Petroleum University (PDPU); частный университет штата, учреждён GSPC
-• Декан по международным связям (по сниппету): Prof. (Dr.) Nigam Dave; общий ящик OIR: oir@pdpu.ac.in
-• Руководитель — Director General (по сниппету Sundar S. Manoharan), официальная страница не открыта
-• Полный почтовый адрес не подтверждён
-• Телефон указан декана по международным связям
-• Спутников не найдено</t>
+• Спутников не найдено
+• Перепроверка: 04.10.2026: на новом домене pdeu.ac.in подтверждены DG, адрес, телефоны и Dean.IR@; руководитель OIR сменился на Prof. Ritu Sharma</t>
         </is>
       </c>
       <c r="AG191" s="4" t="inlineStr">
         <is>
-          <t>• Https://www.pdpu.ac.in/inter-contactus.html
+          <t>• Https://pdeu.ac.in/
+• Https://pdeu.ac.in/contact-us
+• Https://pdeu.ac.in/international-relations
 • Https://en.wikipedia.org/wiki/Pandit_Deendayal_Energy_University
 • Nanosats.eu</t>
         </is>
@@ -34936,7 +35039,7 @@
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t>Periyar University, Salem 636011, Tamil Nadu, India</t>
+          <t>Periyar University, Salem – 636 011, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="J192" s="4" t="inlineStr"/>
@@ -34945,7 +35048,7 @@
       <c r="M192" s="4" t="inlineStr"/>
       <c r="N192" s="4" t="inlineStr">
         <is>
-          <t>+91-427-2345766</t>
+          <t>+91-427-2345766 (General / Registrar Office); +91-427-2346268; +91-427-2346269</t>
         </is>
       </c>
       <c r="O192" s="4" t="inlineStr">
@@ -34990,21 +35093,24 @@
       <c r="AD192" s="4" t="inlineStr"/>
       <c r="AE192" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF192" s="4" t="inlineStr">
         <is>
-          <t>• Должность ректора вакантна: университетом руководит Комитет (Vice-Chancellor Committee) под председательством Thiru P. Ponniah, IAS (комиссар по высшему образованию шт. Тамилнад)
-• На сайте не опубликовано ни одного e-mail — только телефоны (общий 0427-2345766, 2346268, 2346269)
-• Международного офиса не найдено; спутниковых проектов нет</t>
+          <t>• Должность ректора вакантна: университетом руководит Комитет (Vice-Chancellor Committee) под председательством (Convenor) Thiru P. Ponniah, IAS (комиссар по высшему/коллегиальному образованию шт. Тамилнад) — подтверждено на vicechancellor.php 04.10.2026
+• Регистратор (FAC) — Dr. V. Raj (registrar.php)
+• На сайте не опубликовано ни одного e-mail — только телефоны (общий 0427-2345766, 2346268, 2346269); для письма нужен e-mail, полученный по телефону
+• Международного офиса не найдено; спутниковых проектов нет
+• Перепроверка: Сайт открыт 04.10.2026: Комитет VC под председательством Thiru P. Ponniah, IAS, регистратор Dr. V. Raj (FAC) и телефоны подтверждены; e-mail на сайте по-прежнему не опубликован</t>
         </is>
       </c>
       <c r="AG192" s="4" t="inlineStr">
         <is>
           <t>• Https://www.periyaruniversity.ac.in/
 • Https://www.periyaruniversity.ac.in/Contact.php
-• Https://www.periyaruniversity.ac.in/vicechancellor.php</t>
+• Https://www.periyaruniversity.ac.in/vicechancellor.php
+• Https://www.periyaruniversity.ac.in/registrar.php</t>
         </is>
       </c>
       <c r="AH192" s="4" t="inlineStr">
